--- a/data/google-spreadsheet/M3GIM-Organisationsindex.xlsx
+++ b/data/google-spreadsheet/M3GIM-Organisationsindex.xlsx
@@ -11,204 +11,258 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="252">
   <si>
     <t>m3gim_id</t>
   </si>
   <si>
+    <t>Claredon</t>
+  </si>
+  <si>
+    <t>wikidata_id</t>
+  </si>
+  <si>
+    <t>ort</t>
+  </si>
+  <si>
+    <t>Assoziierte Person</t>
+  </si>
+  <si>
+    <t>anmerkung</t>
+  </si>
+  <si>
+    <t>O1</t>
+  </si>
+  <si>
+    <t>Abendkonzerte in Wiener Palais</t>
+  </si>
+  <si>
+    <t>Wien</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>Abendzeitung</t>
+  </si>
+  <si>
+    <t>München</t>
+  </si>
+  <si>
+    <t>Karl Schumann</t>
+  </si>
+  <si>
+    <t>Zeitung</t>
+  </si>
+  <si>
+    <t>O3</t>
+  </si>
+  <si>
+    <t>Académie nationale de musique</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktiengesellschaft Leu &amp; Co. </t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Aktiengesellschaft / Bank</t>
+  </si>
+  <si>
+    <t>O5</t>
+  </si>
+  <si>
+    <t>Arbeiter Zeitung</t>
+  </si>
+  <si>
+    <t>Bauer, Gerhard</t>
+  </si>
+  <si>
+    <t>O6</t>
+  </si>
+  <si>
+    <t>Bayerische Staatsoper</t>
+  </si>
+  <si>
+    <t>Q681931</t>
+  </si>
+  <si>
+    <t>O72</t>
+  </si>
+  <si>
+    <t>Bayreuth (Stadt). Stadtrat</t>
+  </si>
+  <si>
+    <t>Rollwagen, Hans</t>
+  </si>
+  <si>
+    <t>O7</t>
+  </si>
+  <si>
+    <t>Bayreuther Festspiele</t>
+  </si>
+  <si>
+    <t>Q157596</t>
+  </si>
+  <si>
+    <t>Bayreuth</t>
+  </si>
+  <si>
+    <t>Wagner, Wolfgang</t>
+  </si>
+  <si>
+    <t>Klebe, Carl-Heinz</t>
+  </si>
+  <si>
+    <t>Bayreuther Ensemble</t>
+  </si>
+  <si>
+    <t>Bayreuther Festspielorchester</t>
+  </si>
+  <si>
+    <t>Bayrischer Rundfunk</t>
+  </si>
+  <si>
+    <t>O8</t>
+  </si>
+  <si>
+    <t>Centropa Concert Organisation, Konzertdirektion</t>
+  </si>
+  <si>
+    <t>nicht verifizierbar</t>
+  </si>
+  <si>
+    <t>Taubmann, Martin H., Altmann, Olga</t>
+  </si>
+  <si>
+    <t>beide Namen haben dieselbe Adresse, daher zusammengefasst</t>
+  </si>
+  <si>
+    <t>O74</t>
+  </si>
+  <si>
+    <t>Chorgemeinschaft Wuppertal</t>
+  </si>
+  <si>
+    <t>Wuppertal</t>
+  </si>
+  <si>
+    <t>O9</t>
+  </si>
+  <si>
+    <t>Conservatoire</t>
+  </si>
+  <si>
+    <t>Strasbourg</t>
+  </si>
+  <si>
+    <t>O10</t>
+  </si>
+  <si>
+    <t>Convent Garden Opera Company</t>
+  </si>
+  <si>
+    <t>O11</t>
+  </si>
+  <si>
+    <t>Cuvilliéstheater</t>
+  </si>
+  <si>
+    <t>O12</t>
+  </si>
+  <si>
+    <t>Deutsche Oper Berlin</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>O13</t>
+  </si>
+  <si>
+    <t>Deutsches Musikinstitut für Ausländer</t>
+  </si>
+  <si>
+    <t>Berlin-Charlottenburg</t>
+  </si>
+  <si>
+    <t>O14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Düsseldorfer Zeitung </t>
+  </si>
+  <si>
+    <t>Düsseldorf</t>
+  </si>
+  <si>
+    <t>O15</t>
+  </si>
+  <si>
+    <t>Epic Records</t>
+  </si>
+  <si>
+    <t>O16</t>
+  </si>
+  <si>
+    <t>Ernst Kühnly Bühnenvermittlung Inland und Ausland</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Kühnly, Ernst</t>
+  </si>
+  <si>
+    <t>O17</t>
+  </si>
+  <si>
+    <t>Felix Ballhausen Bühnenvermittlung, Ballhaus Agentur München</t>
+  </si>
+  <si>
+    <t>Ballhausen, Felix</t>
+  </si>
+  <si>
+    <t>Francesoir</t>
+  </si>
+  <si>
+    <t>O18</t>
+  </si>
+  <si>
+    <t>Fränkische Presse</t>
+  </si>
+  <si>
+    <t>Dr. Joachim Bergfeld</t>
+  </si>
+  <si>
+    <t>O66</t>
+  </si>
+  <si>
+    <t>Hochschule für Musik und darstellende Kunst Graz</t>
+  </si>
+  <si>
     <t>Graz</t>
   </si>
   <si>
-    <t>wikidata_id</t>
-  </si>
-  <si>
-    <t>ort</t>
-  </si>
-  <si>
-    <t>Assoziierte Person</t>
-  </si>
-  <si>
-    <t>anmerkung</t>
-  </si>
-  <si>
-    <t>O1</t>
-  </si>
-  <si>
-    <t>Abendkonzerte in Wiener Palais</t>
-  </si>
-  <si>
-    <t>Wien</t>
-  </si>
-  <si>
-    <t>O2</t>
-  </si>
-  <si>
-    <t>Abendzeitung</t>
-  </si>
-  <si>
-    <t>München</t>
-  </si>
-  <si>
-    <t>Karl Schumann</t>
-  </si>
-  <si>
-    <t>Zeitung</t>
-  </si>
-  <si>
-    <t>O3</t>
-  </si>
-  <si>
-    <t>Académie nationale de musique</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aktiengesellschaft Leu &amp; Co. </t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
-    <t>Aktiengesellschaft / Bank</t>
-  </si>
-  <si>
-    <t>O5</t>
-  </si>
-  <si>
-    <t>Arbeiter Zeitung</t>
-  </si>
-  <si>
-    <t>Bauer, Gerhard</t>
-  </si>
-  <si>
-    <t>O6</t>
-  </si>
-  <si>
-    <t>Bayerische Staatsoper</t>
-  </si>
-  <si>
-    <t>Q681931</t>
-  </si>
-  <si>
-    <t>O7</t>
-  </si>
-  <si>
-    <t>Bayreuther Festspiele</t>
-  </si>
-  <si>
-    <t>Q157596</t>
-  </si>
-  <si>
-    <t>Bayreuth</t>
-  </si>
-  <si>
-    <t>Wagner, Wolfgang</t>
-  </si>
-  <si>
-    <t>Klebe, Carl-Heinz</t>
-  </si>
-  <si>
-    <t>O8</t>
-  </si>
-  <si>
-    <t>Centropa Concert Organisation, Konzertdirektion</t>
-  </si>
-  <si>
-    <t>nicht verifizierbar</t>
-  </si>
-  <si>
-    <t>Taubmann, Martin H., Altmann, Olga</t>
-  </si>
-  <si>
-    <t>beide Namen haben dieselbe Adresse, daher zusammengefasst</t>
-  </si>
-  <si>
-    <t>O9</t>
-  </si>
-  <si>
-    <t>Conservatoire</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>O10</t>
-  </si>
-  <si>
-    <t>Convent Garden Opera Company</t>
-  </si>
-  <si>
-    <t>O11</t>
-  </si>
-  <si>
-    <t>Cuvilliéstheater</t>
-  </si>
-  <si>
-    <t>O12</t>
-  </si>
-  <si>
-    <t>Deutsche Oper Berlin</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
-    <t>O13</t>
-  </si>
-  <si>
-    <t>Deutsches Musikinstitut für Ausländer</t>
-  </si>
-  <si>
-    <t>Berlin-Charlottenburg</t>
-  </si>
-  <si>
-    <t>O14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Düsseldorfer Zeitung </t>
-  </si>
-  <si>
-    <t>Düsseldorf</t>
-  </si>
-  <si>
-    <t>O15</t>
-  </si>
-  <si>
-    <t>Epic Records</t>
-  </si>
-  <si>
-    <t>O16</t>
-  </si>
-  <si>
-    <t>Ernst Kühnly Bühnenvermittlung Inland und Ausland</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Kühnly, Ernst</t>
-  </si>
-  <si>
-    <t>O17</t>
-  </si>
-  <si>
-    <t>Felix Ballhausen Bühnenvermittlung, Ballhaus Agentur München</t>
-  </si>
-  <si>
-    <t>Ballhausen, Felix</t>
-  </si>
-  <si>
-    <t>O18</t>
-  </si>
-  <si>
-    <t>Fränkische Presse</t>
-  </si>
-  <si>
-    <t>Dr. Joachim Bergfeld</t>
+    <t>Ira Malaniuk</t>
+  </si>
+  <si>
+    <t>O65</t>
+  </si>
+  <si>
+    <t>Indiana University School of Music</t>
+  </si>
+  <si>
+    <t>Bloomington, Indiana</t>
+  </si>
+  <si>
+    <t>Max Röthlisberger</t>
   </si>
   <si>
     <t>O19</t>
@@ -226,6 +280,12 @@
     <t>Hannover</t>
   </si>
   <si>
+    <t xml:space="preserve">Le Figaro </t>
+  </si>
+  <si>
+    <t>Le Journal du Dimanche</t>
+  </si>
+  <si>
     <t>O21</t>
   </si>
   <si>
@@ -235,6 +295,21 @@
     <t>Dumesnil, René</t>
   </si>
   <si>
+    <t>Le Temps de Paris</t>
+  </si>
+  <si>
+    <t>Glotz, Michel</t>
+  </si>
+  <si>
+    <t>Les Nouvelles Littéraires</t>
+  </si>
+  <si>
+    <t>O69</t>
+  </si>
+  <si>
+    <t>Markgräfliches Opernhaus</t>
+  </si>
+  <si>
     <t>O22</t>
   </si>
   <si>
@@ -271,6 +346,12 @@
     <t>Musikakademie in Lemberg</t>
   </si>
   <si>
+    <t>O68</t>
+  </si>
+  <si>
+    <t>Musikverein für Steiermark</t>
+  </si>
+  <si>
     <t>O27</t>
   </si>
   <si>
@@ -328,6 +409,12 @@
     <t>Rundfunk</t>
   </si>
   <si>
+    <t>Nordwestdeutscher Rundfunk</t>
+  </si>
+  <si>
+    <t>Rolf, Wilhelm Alexander</t>
+  </si>
+  <si>
     <t>O33</t>
   </si>
   <si>
@@ -349,6 +436,12 @@
     <t>Opéra de Monte-Carlo. Orchestre national</t>
   </si>
   <si>
+    <t>Opéra Garnier</t>
+  </si>
+  <si>
+    <t>Opéra national de Paris. Orchestre</t>
+  </si>
+  <si>
     <t>O36</t>
   </si>
   <si>
@@ -397,6 +490,27 @@
     <t>R.C.A.-Victor</t>
   </si>
   <si>
+    <t>O79</t>
+  </si>
+  <si>
+    <t>Radio Audizioni Italia (Roma)</t>
+  </si>
+  <si>
+    <t>O71</t>
+  </si>
+  <si>
+    <t>Richard-Wagner-Stipendienstiftung</t>
+  </si>
+  <si>
+    <t>O70</t>
+  </si>
+  <si>
+    <t>Richard-Wagner-Verband</t>
+  </si>
+  <si>
+    <t>Angerer, Dorothea</t>
+  </si>
+  <si>
     <t>O44</t>
   </si>
   <si>
@@ -412,6 +526,12 @@
     <t>Fluggesellschaft</t>
   </si>
   <si>
+    <t>O78</t>
+  </si>
+  <si>
+    <t>Schweizerische Verrechnungsstelle</t>
+  </si>
+  <si>
     <t>O46</t>
   </si>
   <si>
@@ -424,6 +544,12 @@
     <t>Staatsoper Wien</t>
   </si>
   <si>
+    <t>O76</t>
+  </si>
+  <si>
+    <t>Stadthalle Wuppertal-Elberfeld</t>
+  </si>
+  <si>
     <t>O48</t>
   </si>
   <si>
@@ -463,6 +589,24 @@
     <t>K.H. Ruppert</t>
   </si>
   <si>
+    <t>O67</t>
+  </si>
+  <si>
+    <t>Südost-Tagespost</t>
+  </si>
+  <si>
+    <t>Syndicat d'Initiative de la ville de Bruxelles</t>
+  </si>
+  <si>
+    <t>Brüssel</t>
+  </si>
+  <si>
+    <t>Teatro alla Scala</t>
+  </si>
+  <si>
+    <t>Mailand</t>
+  </si>
+  <si>
     <t>O53</t>
   </si>
   <si>
@@ -478,12 +622,21 @@
     <t>Teatro di San Carlo</t>
   </si>
   <si>
+    <t>Théâtre municipal de Lausanne</t>
+  </si>
+  <si>
+    <t>Lausanne</t>
+  </si>
+  <si>
     <t>O55</t>
   </si>
   <si>
     <t>Théâtre National de l'Opéra-Comique</t>
   </si>
   <si>
+    <t>Theatre Royal de la Monnaie</t>
+  </si>
+  <si>
     <t>O56</t>
   </si>
   <si>
@@ -499,6 +652,21 @@
     <t>Salzburg</t>
   </si>
   <si>
+    <t>O77</t>
+  </si>
+  <si>
+    <t>Viva musica</t>
+  </si>
+  <si>
+    <t>Hartmann, Karl Amadeus</t>
+  </si>
+  <si>
+    <t>O75</t>
+  </si>
+  <si>
+    <t>Volksbühne Wuppertal</t>
+  </si>
+  <si>
     <t>O58</t>
   </si>
   <si>
@@ -538,80 +706,74 @@
     <t>k-e-p</t>
   </si>
   <si>
+    <t>O73</t>
+  </si>
+  <si>
+    <t>Wuppertaler Konzertdirektion G. Wylach</t>
+  </si>
+  <si>
     <t>O64</t>
   </si>
   <si>
     <t>Zürcher Tagblatt</t>
   </si>
   <si>
-    <t>O65</t>
-  </si>
-  <si>
-    <t>Indiana University School of Music</t>
-  </si>
-  <si>
-    <t>Bloomington, Indiana</t>
-  </si>
-  <si>
-    <t>Max Röthlisberger</t>
-  </si>
-  <si>
-    <t>O66</t>
-  </si>
-  <si>
-    <t>Hochschule für Musik und darstellende Kunst Graz</t>
-  </si>
-  <si>
-    <t>Ira Malaniuk</t>
-  </si>
-  <si>
-    <t>O67</t>
-  </si>
-  <si>
-    <t>Südost-Tagespost</t>
-  </si>
-  <si>
-    <t>O68</t>
-  </si>
-  <si>
-    <t>Musikverein für Steiermark</t>
-  </si>
-  <si>
-    <t>O69</t>
-  </si>
-  <si>
-    <t>Markgräfliches Opernhaus</t>
-  </si>
-  <si>
-    <t>O70</t>
-  </si>
-  <si>
-    <t>Richard-Wagner-Verband</t>
-  </si>
-  <si>
-    <t>Angerer, Dorothea</t>
-  </si>
-  <si>
-    <t>O71</t>
-  </si>
-  <si>
-    <t>Richard-Wagner-Stipendienstiftung</t>
-  </si>
-  <si>
-    <t>O72</t>
-  </si>
-  <si>
-    <t>O73</t>
-  </si>
-  <si>
-    <t>O74</t>
+    <t>Radio Audizioni Italia. Coro di Torino</t>
+  </si>
+  <si>
+    <t>Turin</t>
+  </si>
+  <si>
+    <t>Radiotelevisione italiana</t>
+  </si>
+  <si>
+    <t>Die Presse</t>
+  </si>
+  <si>
+    <t>Dr. Erwin Mittag</t>
+  </si>
+  <si>
+    <t>Das Musikleben</t>
+  </si>
+  <si>
+    <t>Müller-Minervo, Otto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teldec </t>
+  </si>
+  <si>
+    <t>Plattenlabel</t>
+  </si>
+  <si>
+    <t>Columbia Graphophone</t>
+  </si>
+  <si>
+    <t>Grand Hotel Brüssel</t>
+  </si>
+  <si>
+    <t>Radio Monte Carlo</t>
+  </si>
+  <si>
+    <t>Jaumonet, Leopold</t>
+  </si>
+  <si>
+    <t>Deutsches Museum von Meisterwerken der Naturwissenschaft und Technik</t>
+  </si>
+  <si>
+    <t>Süddeutscher Rundfunk</t>
+  </si>
+  <si>
+    <t>Hessischer Rundfunk</t>
+  </si>
+  <si>
+    <t>Frankfurt a.M.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -638,6 +800,17 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="9.0"/>
@@ -691,14 +864,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -708,7 +881,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -720,29 +893,38 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1089,810 +1271,1100 @@
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="E8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="D11" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5"/>
+      <c r="B12" s="10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5"/>
+      <c r="B13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>44</v>
+      <c r="D13" s="10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>13</v>
+        <v>47</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="9"/>
+        <v>52</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="E23" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>13</v>
-      </c>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>75</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>77</v>
+      <c r="A25" s="5"/>
+      <c r="B25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="12" t="s">
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="5"/>
+      <c r="B31" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D31" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="5"/>
+      <c r="B32" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="D32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>104</v>
+      <c r="A34" s="5"/>
+      <c r="B34" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>1</v>
+      <c r="A35" s="5"/>
+      <c r="B35" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>109</v>
+        <v>97</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>109</v>
+        <v>99</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>40</v>
+        <v>103</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>117</v>
+        <v>106</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>8</v>
+        <v>109</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>121</v>
+        <v>111</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>123</v>
+        <v>113</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>11</v>
+        <v>116</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>127</v>
+        <v>119</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>129</v>
+        <v>122</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="5"/>
+      <c r="B49" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="5"/>
+      <c r="B53" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="D53" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="5"/>
+      <c r="B54" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>149</v>
+      <c r="D54" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>152</v>
+        <v>143</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>156</v>
+        <v>147</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>19</v>
+        <v>149</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>161</v>
+        <v>151</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>8</v>
+        <v>153</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>8</v>
+        <v>155</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>8</v>
+        <v>157</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>8</v>
+        <v>159</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>171</v>
+        <v>161</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B68" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="D68" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="B69" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E65" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="F65" s="11" t="s">
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F74" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D66" s="11" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="B78" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="B79" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D85" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F66" s="11" t="s">
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F94" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F69" s="11" t="s">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="11" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="B97" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="B98" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="B99" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="B100" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="B101" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="B103" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="B104" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="B105" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="B106" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="B107" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="B108" s="10"/>
+      <c r="D108" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
     <row r="109" ht="15.75" customHeight="1"/>
     <row r="110" ht="15.75" customHeight="1"/>
     <row r="111" ht="15.75" customHeight="1"/>
@@ -2785,6 +3257,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
